--- a/experiment/ELAN_bestx2/Test/results_table.xlsx
+++ b/experiment/ELAN_bestx2/Test/results_table.xlsx
@@ -565,43 +565,43 @@
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">
-2,298K</t>
+1,304K</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>34.706/
-0.9415</t>
+          <t>37.915/
+0.9601</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>31.196/
-0.8936</t>
+          <t>33.507/
+0.9171</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>30.331/
-0.8736</t>
+          <t>32.136/
+0.8995</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>27.689/
-0.8676</t>
+          <t>31.895/
+0.9262</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>32.291/
-0.9496</t>
+          <t>38.361/
+0.9762</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>31.243/
-0.9052</t>
+          <t>34.763/
+0.9358</t>
         </is>
       </c>
     </row>
